--- a/data/trans_dic/IP13_R2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas</t>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,35</t>
+          <t>1,02; 6,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,16</t>
+          <t>0,67; 5,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,75</t>
+          <t>1,16; 4,82</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 9,54</t>
+          <t>1,6; 8,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,97</t>
+          <t>3,4; 12,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,44</t>
+          <t>3,35; 8,72</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 9,19</t>
+          <t>0,76; 9,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,56</t>
+          <t>1,35; 11,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,22</t>
+          <t>1,73; 8,11</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,19</t>
+          <t>1,26; 5,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,38</t>
+          <t>2,97; 8,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,06</t>
+          <t>2,53; 6,01</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 11,77</t>
+          <t>4,11; 11,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,98</t>
+          <t>2,31; 8,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,3</t>
+          <t>3,52; 8,44</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 10,43</t>
+          <t>1,47; 9,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,04</t>
+          <t>1,18; 11,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,19</t>
+          <t>2,08; 8,25</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,63</t>
+          <t>2,96; 5,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,12</t>
+          <t>3,42; 6,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,47</t>
+          <t>3,46; 5,4</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1070; 6700</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>915; 7818</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2780; 11587</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4364</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6356</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10719</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1511; 8438</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3247; 11938</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6382; 16584</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1687</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4591</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>395; 4947</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>859; 7336</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1997; 9385</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6148</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11528</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17676</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2748; 11271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6489; 18479</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11042; 26218</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8865</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16069</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4910; 14283</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3750; 13902</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9924; 23818</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2928</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1011; 6849</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>847; 8065</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2934; 11631</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>26858</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>34744</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>61602</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>19435; 35364</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25591; 46747</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>48675; 75887</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,41</t>
+          <t>0,97; 6,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,74</t>
+          <t>0,64; 6,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,82</t>
+          <t>1,15; 4,57</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,91</t>
+          <t>1,6; 9,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 12,49</t>
+          <t>3,21; 11,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,72</t>
+          <t>3,25; 8,99</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 9,54</t>
+          <t>0,75; 9,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,49</t>
+          <t>1,28; 10,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,11</t>
+          <t>1,81; 8,48</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,17</t>
+          <t>1,21; 5,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,47</t>
+          <t>3,11; 8,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,01</t>
+          <t>2,53; 5,94</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,96</t>
+          <t>4,16; 12,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,55</t>
+          <t>2,08; 8,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,44</t>
+          <t>3,78; 8,51</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 9,94</t>
+          <t>1,39; 9,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,2</t>
+          <t>1,22; 11,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,25</t>
+          <t>2,1; 7,96</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,38</t>
+          <t>3,02; 5,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,25</t>
+          <t>3,37; 6,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,4</t>
+          <t>3,41; 5,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1070; 6700</t>
+          <t>1013; 6856</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>915; 7818</t>
+          <t>870; 8405</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2780; 11587</t>
+          <t>2764; 11006</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1511; 8438</t>
+          <t>1513; 8998</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3247; 11938</t>
+          <t>3063; 11063</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6382; 16584</t>
+          <t>6181; 17110</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>395; 4947</t>
+          <t>391; 4708</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>859; 7336</t>
+          <t>814; 6403</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1997; 9385</t>
+          <t>2093; 9811</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2748; 11271</t>
+          <t>2643; 11829</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6489; 18479</t>
+          <t>6787; 18963</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11042; 26218</t>
+          <t>11039; 25932</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4910; 14283</t>
+          <t>4965; 14736</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3750; 13902</t>
+          <t>3389; 13321</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9924; 23818</t>
+          <t>10654; 24008</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1011; 6849</t>
+          <t>957; 6424</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>847; 8065</t>
+          <t>882; 8191</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2934; 11631</t>
+          <t>2957; 11216</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19435; 35364</t>
+          <t>19825; 36416</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25591; 46747</t>
+          <t>25220; 45072</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48675; 75887</t>
+          <t>47974; 74879</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,56</t>
+          <t>0,71; 6,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,17</t>
+          <t>1,16; 6,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,57</t>
+          <t>1,18; 5,13</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 9,5</t>
+          <t>3,46; 12,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,58</t>
+          <t>1,66; 9,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,99</t>
+          <t>3,4; 9,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 9,08</t>
+          <t>1,56; 13,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,03</t>
+          <t>0,66; 8,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,48</t>
+          <t>1,62; 8,5</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,43</t>
+          <t>2,71; 8,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,69</t>
+          <t>1,58; 6,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,94</t>
+          <t>2,73; 6,19</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,34</t>
+          <t>2,5; 8,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,19</t>
+          <t>3,96; 11,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,51</t>
+          <t>3,67; 8,41</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 9,32</t>
+          <t>1,33; 12,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,38</t>
+          <t>1,44; 10,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,96</t>
+          <t>2,2; 8,56</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,54</t>
+          <t>3,4; 6,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,02</t>
+          <t>3,14; 5,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,33</t>
+          <t>3,69; 5,65</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6096</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1013; 6856</t>
+          <t>871; 8035</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>870; 8405</t>
+          <t>1193; 6833</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2764; 11006</t>
+          <t>2665; 11532</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10622</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1513; 8998</t>
+          <t>3166; 11562</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3063; 11063</t>
+          <t>1600; 8979</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6181; 17110</t>
+          <t>6388; 17789</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4592</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>391; 4708</t>
+          <t>889; 7528</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>814; 6403</t>
+          <t>355; 4598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2093; 9811</t>
+          <t>1793; 9381</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>16026</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2643; 11829</t>
+          <t>5478; 16232</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6787; 18963</t>
+          <t>2833; 11033</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11039; 25932</t>
+          <t>10381; 23555</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>14993</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4965; 14736</t>
+          <t>3707; 12231</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3389; 13321</t>
+          <t>4703; 13535</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10654; 24008</t>
+          <t>9787; 22445</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6594</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>957; 6424</t>
+          <t>909; 8289</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>882; 8191</t>
+          <t>1011; 7593</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2957; 11216</t>
+          <t>3045; 11870</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34744</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>58924</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19825; 36416</t>
+          <t>23399; 43240</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25220; 45072</t>
+          <t>19506; 35958</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47974; 74879</t>
+          <t>48267; 74030</t>
         </is>
       </c>
     </row>
